--- a/Shared/XLS/Shop.xlsx
+++ b/Shared/XLS/Shop.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="16290" windowHeight="9060" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="16290" windowHeight="9060" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="109">
   <si>
     <t>!Enum</t>
   </si>
@@ -321,6 +321,30 @@
   </si>
   <si>
     <t>재료2</t>
+  </si>
+  <si>
+    <t>고양이1</t>
+  </si>
+  <si>
+    <t>고양이2</t>
+  </si>
+  <si>
+    <t>고양이3</t>
+  </si>
+  <si>
+    <t>고양이4</t>
+  </si>
+  <si>
+    <t>고양이5</t>
+  </si>
+  <si>
+    <t>고양이6</t>
+  </si>
+  <si>
+    <t>토끼 코스튬</t>
+  </si>
+  <si>
+    <t>요술봉</t>
   </si>
 </sst>
 </file>
@@ -1095,7 +1119,7 @@
         <v>4</v>
       </c>
       <c r="E7" s="10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1281,7 +1305,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="9" customWidth="1"/>
@@ -2119,6 +2143,270 @@
         <v>1</v>
       </c>
     </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B28" s="10">
+        <v>25</v>
+      </c>
+      <c r="C28" s="10">
+        <v>401</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I28">
+        <v>4101</v>
+      </c>
+      <c r="J28" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K28" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="L28" s="10">
+        <v>2000</v>
+      </c>
+      <c r="M28" s="10">
+        <v>1</v>
+      </c>
+      <c r="N28"/>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B29" s="10">
+        <v>26</v>
+      </c>
+      <c r="C29" s="10">
+        <v>401</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I29">
+        <v>4102</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K29" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="L29" s="10">
+        <v>2000</v>
+      </c>
+      <c r="M29" s="10">
+        <v>1</v>
+      </c>
+      <c r="N29"/>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B30" s="10">
+        <v>27</v>
+      </c>
+      <c r="C30" s="10">
+        <v>401</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I30">
+        <v>4103</v>
+      </c>
+      <c r="J30" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K30" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="L30" s="10">
+        <v>2000</v>
+      </c>
+      <c r="M30" s="10">
+        <v>1</v>
+      </c>
+      <c r="N30"/>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B31" s="10">
+        <v>28</v>
+      </c>
+      <c r="C31" s="10">
+        <v>401</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I31">
+        <v>4104</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K31" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="L31" s="10">
+        <v>2000</v>
+      </c>
+      <c r="M31" s="10">
+        <v>1</v>
+      </c>
+      <c r="N31"/>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B32" s="10">
+        <v>29</v>
+      </c>
+      <c r="C32" s="10">
+        <v>401</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I32">
+        <v>4105</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K32" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="L32" s="10">
+        <v>2000</v>
+      </c>
+      <c r="M32" s="10">
+        <v>1</v>
+      </c>
+      <c r="N32"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B33" s="10">
+        <v>30</v>
+      </c>
+      <c r="C33" s="10">
+        <v>401</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I33">
+        <v>4106</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K33" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="L33" s="10">
+        <v>2000</v>
+      </c>
+      <c r="M33" s="10">
+        <v>1</v>
+      </c>
+      <c r="N33"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B34" s="10">
+        <v>31</v>
+      </c>
+      <c r="C34" s="10">
+        <v>501</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I34">
+        <v>4201</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K34" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="L34" s="10">
+        <v>3000</v>
+      </c>
+      <c r="M34" s="10">
+        <v>1</v>
+      </c>
+      <c r="N34"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B35" s="10">
+        <v>32</v>
+      </c>
+      <c r="C35" s="10">
+        <v>501</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I35">
+        <v>4202</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K35" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="L35" s="10">
+        <v>2500</v>
+      </c>
+      <c r="M35" s="10">
+        <v>1</v>
+      </c>
+      <c r="N35"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Shared/XLS/Shop.xlsx
+++ b/Shared/XLS/Shop.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="113">
   <si>
     <t>!Enum</t>
   </si>
@@ -76,9 +76,6 @@
     <t>!EnumTable</t>
   </si>
   <si>
-    <t>ShopCategory</t>
-  </si>
-  <si>
     <t>!ID</t>
   </si>
   <si>
@@ -130,18 +127,9 @@
     <t>코스튬</t>
   </si>
   <si>
-    <t>AdShop</t>
-  </si>
-  <si>
-    <t>광고상품</t>
-  </si>
-  <si>
     <t>!Table</t>
   </si>
   <si>
-    <t>ShopGoodsGroup</t>
-  </si>
-  <si>
     <t>Category</t>
   </si>
   <si>
@@ -152,9 +140,6 @@
   </si>
   <si>
     <t>루비</t>
-  </si>
-  <si>
-    <t>광고 상품</t>
   </si>
   <si>
     <t>ShopGoods</t>
@@ -311,18 +296,6 @@
     <t>루비 600000 상품</t>
   </si>
   <si>
-    <t>광고 재료1</t>
-  </si>
-  <si>
-    <t>재료1</t>
-  </si>
-  <si>
-    <t>광고 재료2</t>
-  </si>
-  <si>
-    <t>재료2</t>
-  </si>
-  <si>
     <t>고양이1</t>
   </si>
   <si>
@@ -345,18 +318,77 @@
   </si>
   <si>
     <t>요술봉</t>
+  </si>
+  <si>
+    <t>ShopGoodsGroup</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShopCategory</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>지식의 서</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>지식의 서 x5</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>지식의 서 x10</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬포인트를 1개 획득합니다.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬포인트를 5개 획득합니다.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬포인트를 10개 획득합니다.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_SkillBook</t>
+  </si>
+  <si>
+    <t>Etc</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -546,48 +578,57 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -596,28 +637,22 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -892,7 +927,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1006,7 +1041,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -1028,47 +1063,47 @@
       <c r="A1" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="13" t="s">
-        <v>19</v>
+      <c r="B1" s="23" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="E2" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="E3" s="10" t="s">
         <v>26</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="B4" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>28</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>29</v>
       </c>
       <c r="D4" s="10">
         <v>1</v>
@@ -1083,7 +1118,7 @@
         <v>12</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="10">
         <v>2</v>
@@ -1095,10 +1130,10 @@
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>31</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>32</v>
       </c>
       <c r="D6" s="10">
         <v>3</v>
@@ -1110,10 +1145,10 @@
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>34</v>
       </c>
       <c r="D7" s="10">
         <v>4</v>
@@ -1124,10 +1159,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B8" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
         <v>35</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
       </c>
       <c r="D8" s="10">
         <v>5</v>
@@ -1138,10 +1173,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>38</v>
+        <v>103</v>
       </c>
       <c r="D9" s="10">
         <v>6</v>
@@ -1151,7 +1186,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -1173,35 +1208,35 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>40</v>
+        <v>36</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>100</v>
       </c>
       <c r="C1" s="13"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>20</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>24</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1210,10 +1245,10 @@
         <v>101</v>
       </c>
       <c r="C4" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>28</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1222,10 +1257,10 @@
         <v>201</v>
       </c>
       <c r="C5" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>31</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -1236,7 +1271,7 @@
         <v>12</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -1248,7 +1283,7 @@
         <v>12</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -1260,7 +1295,7 @@
         <v>12</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -1268,10 +1303,10 @@
         <v>401</v>
       </c>
       <c r="C9" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -1279,10 +1314,10 @@
         <v>501</v>
       </c>
       <c r="C10" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>35</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -1290,14 +1325,14 @@
         <v>601</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>45</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -1305,7 +1340,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="9" customWidth="1"/>
@@ -1326,95 +1361,95 @@
   <sheetData>
     <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C1" s="13"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>21</v>
-      </c>
       <c r="E2" s="14" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>1</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="J2" s="10" t="s">
         <v>14</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="N2" s="18" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" s="17" t="s">
         <v>26</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="I3" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N3" s="17" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -1426,13 +1461,13 @@
         <v>101</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H4" t="s">
         <v>2</v>
@@ -1458,10 +1493,10 @@
         <v>5</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="H5" t="s">
         <v>4</v>
@@ -1484,10 +1519,10 @@
         <v>101</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="H6" t="s">
         <v>6</v>
@@ -1499,7 +1534,7 @@
         <v>12</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="L6" s="10">
         <v>5000</v>
@@ -1516,10 +1551,10 @@
         <v>101</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="H7" t="s">
         <v>6</v>
@@ -1531,7 +1566,7 @@
         <v>12</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="L7" s="10">
         <v>5000</v>
@@ -1548,13 +1583,13 @@
         <v>201</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H8" s="10" t="s">
         <v>8</v>
@@ -1580,13 +1615,13 @@
         <v>201</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H9" s="10" t="s">
         <v>8</v>
@@ -1613,13 +1648,13 @@
         <v>201</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H10" s="10" t="s">
         <v>8</v>
@@ -1646,13 +1681,13 @@
         <v>301</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H11" t="s">
         <v>12</v>
@@ -1675,16 +1710,16 @@
         <v>301</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F12" s="21">
         <v>2</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s">
         <v>12</v>
@@ -1707,16 +1742,16 @@
         <v>301</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F13" s="21">
         <v>4</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H13" t="s">
         <v>12</v>
@@ -1739,16 +1774,16 @@
         <v>301</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F14" s="21">
         <v>6</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s">
         <v>12</v>
@@ -1771,16 +1806,16 @@
         <v>301</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F15" s="21">
         <v>8</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s">
         <v>12</v>
@@ -1803,10 +1838,10 @@
         <v>302</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s">
         <v>12</v>
@@ -1832,10 +1867,10 @@
         <v>302</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F17" s="21">
         <v>2</v>
@@ -1861,10 +1896,10 @@
         <v>302</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="F18" s="21">
         <v>4</v>
@@ -1890,10 +1925,10 @@
         <v>302</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F19" s="21">
         <v>6</v>
@@ -1919,10 +1954,10 @@
         <v>302</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="F20" s="21">
         <v>8</v>
@@ -1948,10 +1983,10 @@
         <v>303</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="H21" t="s">
         <v>12</v>
@@ -1977,10 +2012,10 @@
         <v>303</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F22" s="21">
         <v>2</v>
@@ -2006,10 +2041,10 @@
         <v>303</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F23" s="21">
         <v>4</v>
@@ -2035,10 +2070,10 @@
         <v>303</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F24" s="21">
         <v>6</v>
@@ -2064,10 +2099,10 @@
         <v>303</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="F25" s="21">
         <v>8</v>
@@ -2093,26 +2128,30 @@
         <v>601</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>98</v>
+        <v>108</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>111</v>
       </c>
       <c r="H26" s="10" t="s">
         <v>10</v>
       </c>
       <c r="I26">
-        <v>4016</v>
+        <v>4301</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="M26" s="10">
-        <v>1</v>
-      </c>
-      <c r="N26" t="b">
-        <v>1</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="K26" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="L26" s="10">
+        <v>10000</v>
+      </c>
+      <c r="N26"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B27" s="10">
@@ -2122,57 +2161,67 @@
         <v>601</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>100</v>
+        <v>109</v>
+      </c>
+      <c r="F27" s="21">
+        <v>2</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>111</v>
       </c>
       <c r="H27" s="10" t="s">
         <v>10</v>
       </c>
       <c r="I27">
-        <v>4017</v>
+        <v>4302</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="M27" s="10">
-        <v>1</v>
-      </c>
-      <c r="N27" t="b">
-        <v>1</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="K27" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="L27" s="10">
+        <v>25000</v>
+      </c>
+      <c r="N27"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B28" s="10">
         <v>25</v>
       </c>
       <c r="C28" s="10">
-        <v>401</v>
+        <v>601</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>101</v>
+        <v>110</v>
+      </c>
+      <c r="F28" s="21">
+        <v>4</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>111</v>
       </c>
       <c r="H28" s="10" t="s">
         <v>10</v>
       </c>
       <c r="I28">
-        <v>4101</v>
+        <v>4303</v>
       </c>
       <c r="J28" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="L28" s="10">
-        <v>2000</v>
-      </c>
-      <c r="M28" s="10">
-        <v>1</v>
+        <v>40000</v>
       </c>
       <c r="N28"/>
     </row>
@@ -2184,22 +2233,22 @@
         <v>401</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="H29" s="10" t="s">
         <v>10</v>
       </c>
       <c r="I29">
-        <v>4102</v>
+        <v>4101</v>
       </c>
       <c r="J29" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="L29" s="10">
         <v>2000</v>
@@ -2217,22 +2266,22 @@
         <v>401</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="H30" s="10" t="s">
         <v>10</v>
       </c>
       <c r="I30">
-        <v>4103</v>
+        <v>4102</v>
       </c>
       <c r="J30" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="L30" s="10">
         <v>2000</v>
@@ -2250,22 +2299,22 @@
         <v>401</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="H31" s="10" t="s">
         <v>10</v>
       </c>
       <c r="I31">
-        <v>4104</v>
+        <v>4103</v>
       </c>
       <c r="J31" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="L31" s="10">
         <v>2000</v>
@@ -2283,22 +2332,22 @@
         <v>401</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="H32" s="10" t="s">
         <v>10</v>
       </c>
       <c r="I32">
-        <v>4105</v>
+        <v>4104</v>
       </c>
       <c r="J32" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="L32" s="10">
         <v>2000</v>
@@ -2316,22 +2365,22 @@
         <v>401</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="H33" s="10" t="s">
         <v>10</v>
       </c>
       <c r="I33">
-        <v>4106</v>
+        <v>4105</v>
       </c>
       <c r="J33" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="L33" s="10">
         <v>2000</v>
@@ -2346,28 +2395,28 @@
         <v>31</v>
       </c>
       <c r="C34" s="10">
-        <v>501</v>
+        <v>401</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="H34" s="10" t="s">
         <v>10</v>
       </c>
       <c r="I34">
-        <v>4201</v>
+        <v>4106</v>
       </c>
       <c r="J34" s="10" t="s">
         <v>12</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="L34" s="10">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="M34" s="10">
         <v>1</v>
@@ -2382,33 +2431,66 @@
         <v>501</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="H35" s="10" t="s">
         <v>10</v>
       </c>
       <c r="I35">
+        <v>4201</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K35" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="L35" s="10">
+        <v>3000</v>
+      </c>
+      <c r="M35" s="10">
+        <v>1</v>
+      </c>
+      <c r="N35"/>
+    </row>
+    <row r="36" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B36" s="10">
+        <v>33</v>
+      </c>
+      <c r="C36" s="10">
+        <v>501</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I36">
         <v>4202</v>
       </c>
-      <c r="J35" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K35" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="L35" s="10">
+      <c r="J36" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K36" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="L36" s="10">
         <v>2500</v>
       </c>
-      <c r="M35" s="10">
-        <v>1</v>
-      </c>
-      <c r="N35"/>
+      <c r="M36" s="10">
+        <v>1</v>
+      </c>
+      <c r="N36"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/Shared/XLS/Shop.xlsx
+++ b/Shared/XLS/Shop.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="127">
   <si>
     <t>!Enum</t>
   </si>
@@ -368,6 +368,61 @@
   </si>
   <si>
     <t>Etc</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>보관함</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>인벤토리 보관함을 10개 확장합니다.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ruby</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>InventorySlot</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>StashSlot</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>인벤토리 슬롯</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>창고 슬롯</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>창고 보관함을 5개 확장합니다.</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>GoodsValue</t>
+  </si>
+  <si>
+    <t>ShopItem_InventorySlot</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShopItem_StashSlot</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>인벤토리 슬롯</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>창고 슬롯</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -935,7 +990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="9" bestFit="1" customWidth="1"/>
@@ -1006,37 +1061,53 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B10" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B11" s="10" t="s">
-        <v>10</v>
-      </c>
+      <c r="C11" s="11"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" s="10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13" s="10" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B14" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B15" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B16" s="10" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1194,7 +1265,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="9" customWidth="1"/>
@@ -1331,6 +1402,17 @@
         <v>104</v>
       </c>
     </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B12" s="10">
+        <v>602</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>114</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1340,26 +1422,26 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="9" customWidth="1"/>
     <col min="2" max="2" width="11.5" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.75" style="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.5" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.375" style="10" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="10" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.625" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.875" style="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.5" style="10" bestFit="1" customWidth="1"/>
     <col min="10" max="12" width="10.875" style="10" customWidth="1"/>
     <col min="13" max="13" width="18.875" style="10" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="9" style="10" customWidth="1"/>
+    <col min="14" max="15" width="13.75" style="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="9" style="10" customWidth="1"/>
     <col min="18" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
@@ -1368,7 +1450,7 @@
       </c>
       <c r="C1" s="13"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
         <v>19</v>
@@ -1409,8 +1491,11 @@
       <c r="N2" s="18" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O2" s="18" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="7" t="s">
         <v>25</v>
@@ -1451,8 +1536,11 @@
       <c r="N3" s="17" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O3" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="B4" s="10">
         <v>1</v>
@@ -1482,7 +1570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="10">
         <v>2</v>
       </c>
@@ -1511,7 +1599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" s="10">
         <v>3</v>
       </c>
@@ -1543,7 +1631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" s="10">
         <v>4</v>
       </c>
@@ -1575,7 +1663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B8" s="10">
         <v>5</v>
       </c>
@@ -1607,7 +1695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B9" s="10">
         <v>6</v>
       </c>
@@ -1639,7 +1727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
       <c r="B10" s="10">
         <v>7</v>
@@ -1672,7 +1760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="B11" s="10">
         <v>8</v>
@@ -1702,7 +1790,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B12" s="10">
         <v>9</v>
       </c>
@@ -1734,7 +1822,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B13" s="10">
         <v>10</v>
       </c>
@@ -1766,7 +1854,7 @@
         <v>21000</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B14" s="10">
         <v>11</v>
       </c>
@@ -1798,7 +1886,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B15" s="10">
         <v>12</v>
       </c>
@@ -1830,7 +1918,7 @@
         <v>39000</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B16" s="10">
         <v>13</v>
       </c>
@@ -1858,8 +1946,9 @@
       <c r="N16" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="O16"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B17" s="10">
         <v>14</v>
       </c>
@@ -1888,7 +1977,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B18" s="10">
         <v>15</v>
       </c>
@@ -1917,7 +2006,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B19" s="10">
         <v>16</v>
       </c>
@@ -1946,7 +2035,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B20" s="10">
         <v>17</v>
       </c>
@@ -1975,7 +2064,7 @@
         <v>29000</v>
       </c>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B21" s="10">
         <v>18</v>
       </c>
@@ -2003,8 +2092,9 @@
       <c r="N21" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="O21"/>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B22" s="10">
         <v>19</v>
       </c>
@@ -2033,7 +2123,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B23" s="10">
         <v>20</v>
       </c>
@@ -2062,7 +2152,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B24" s="10">
         <v>21</v>
       </c>
@@ -2091,7 +2181,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B25" s="10">
         <v>22</v>
       </c>
@@ -2120,7 +2210,7 @@
         <v>29000</v>
       </c>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B26" s="10">
         <v>23</v>
       </c>
@@ -2152,8 +2242,9 @@
         <v>10000</v>
       </c>
       <c r="N26"/>
-    </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="O26"/>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B27" s="10">
         <v>24</v>
       </c>
@@ -2188,8 +2279,9 @@
         <v>25000</v>
       </c>
       <c r="N27"/>
-    </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="O27"/>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B28" s="10">
         <v>25</v>
       </c>
@@ -2224,8 +2316,9 @@
         <v>40000</v>
       </c>
       <c r="N28"/>
-    </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="O28"/>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B29" s="10">
         <v>26</v>
       </c>
@@ -2257,8 +2350,9 @@
         <v>1</v>
       </c>
       <c r="N29"/>
-    </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="O29"/>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B30" s="10">
         <v>27</v>
       </c>
@@ -2290,8 +2384,9 @@
         <v>1</v>
       </c>
       <c r="N30"/>
-    </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="O30"/>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B31" s="10">
         <v>28</v>
       </c>
@@ -2323,8 +2418,9 @@
         <v>1</v>
       </c>
       <c r="N31"/>
-    </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="O31"/>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B32" s="10">
         <v>29</v>
       </c>
@@ -2356,8 +2452,9 @@
         <v>1</v>
       </c>
       <c r="N32"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="O32"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B33" s="10">
         <v>30</v>
       </c>
@@ -2389,8 +2486,9 @@
         <v>1</v>
       </c>
       <c r="N33"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="O33"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B34" s="10">
         <v>31</v>
       </c>
@@ -2422,8 +2520,9 @@
         <v>1</v>
       </c>
       <c r="N34"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="O34"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B35" s="10">
         <v>32</v>
       </c>
@@ -2455,8 +2554,9 @@
         <v>1</v>
       </c>
       <c r="N35"/>
-    </row>
-    <row r="36" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="O35"/>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B36" s="10">
         <v>33</v>
       </c>
@@ -2488,6 +2588,77 @@
         <v>1</v>
       </c>
       <c r="N36"/>
+      <c r="O36"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B37" s="10">
+        <v>34</v>
+      </c>
+      <c r="C37" s="10">
+        <v>602</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="H37" t="s">
+        <v>117</v>
+      </c>
+      <c r="J37" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K37" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="L37" s="10">
+        <v>10000</v>
+      </c>
+      <c r="M37" s="10">
+        <v>10</v>
+      </c>
+      <c r="O37" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B38" s="10">
+        <v>35</v>
+      </c>
+      <c r="C38" s="10">
+        <v>602</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="H38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J38" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K38" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="L38" s="10">
+        <v>10000</v>
+      </c>
+      <c r="M38" s="10">
+        <v>10</v>
+      </c>
+      <c r="O38" s="10">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>

--- a/Shared/XLS/Shop.xlsx
+++ b/Shared/XLS/Shop.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="16290" windowHeight="9060" activeTab="3"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="16290" windowHeight="9060" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="129">
   <si>
     <t>!Enum</t>
   </si>
@@ -423,6 +423,14 @@
   </si>
   <si>
     <t>창고 슬롯</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>보물</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>특가</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -982,7 +990,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1174,7 +1182,7 @@
         <v>27</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="D4" s="10">
         <v>1</v>
@@ -1204,7 +1212,7 @@
         <v>30</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>31</v>
+        <v>127</v>
       </c>
       <c r="D6" s="10">
         <v>3</v>
